--- a/data/nzd0141/nzd0141.xlsx
+++ b/data/nzd0141/nzd0141.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L605"/>
+  <dimension ref="A1:L607"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25854,6 +25854,90 @@
         <v>332.49</v>
       </c>
       <c r="L605" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:12:09+00:00</t>
+        </is>
+      </c>
+      <c r="B606" t="n">
+        <v>315.18</v>
+      </c>
+      <c r="C606" t="n">
+        <v>313.62</v>
+      </c>
+      <c r="D606" t="n">
+        <v>323.68</v>
+      </c>
+      <c r="E606" t="n">
+        <v>331.92</v>
+      </c>
+      <c r="F606" t="n">
+        <v>335.93</v>
+      </c>
+      <c r="G606" t="n">
+        <v>335.74</v>
+      </c>
+      <c r="H606" t="n">
+        <v>343.57</v>
+      </c>
+      <c r="I606" t="n">
+        <v>346.42</v>
+      </c>
+      <c r="J606" t="n">
+        <v>340.98</v>
+      </c>
+      <c r="K606" t="n">
+        <v>331.69</v>
+      </c>
+      <c r="L606" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:06:18+00:00</t>
+        </is>
+      </c>
+      <c r="B607" t="n">
+        <v>316.43</v>
+      </c>
+      <c r="C607" t="n">
+        <v>314.16</v>
+      </c>
+      <c r="D607" t="n">
+        <v>324.4</v>
+      </c>
+      <c r="E607" t="n">
+        <v>333.09</v>
+      </c>
+      <c r="F607" t="n">
+        <v>336.56</v>
+      </c>
+      <c r="G607" t="n">
+        <v>336.97</v>
+      </c>
+      <c r="H607" t="n">
+        <v>344.04</v>
+      </c>
+      <c r="I607" t="n">
+        <v>346.94</v>
+      </c>
+      <c r="J607" t="n">
+        <v>341.29</v>
+      </c>
+      <c r="K607" t="n">
+        <v>332.22</v>
+      </c>
+      <c r="L607" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -25870,7 +25954,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B619"/>
+  <dimension ref="A1:B621"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32063,6 +32147,26 @@
       </c>
       <c r="B619" t="n">
         <v>0.68</v>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B620" t="n">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B621" t="n">
+        <v>1.4</v>
       </c>
     </row>
   </sheetData>
@@ -32231,28 +32335,28 @@
         <v>0.0356</v>
       </c>
       <c r="I2" t="n">
-        <v>0.006589250762393593</v>
+        <v>0.003061211719461946</v>
       </c>
       <c r="J2" t="n">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="K2" t="n">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0001385882598716748</v>
+        <v>2.998888405980615e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>3.141498166172889</v>
+        <v>3.145885400345232</v>
       </c>
       <c r="N2" t="n">
-        <v>16.85079596424581</v>
+        <v>16.8833943507199</v>
       </c>
       <c r="O2" t="n">
-        <v>4.104972102736609</v>
+        <v>4.108940782089698</v>
       </c>
       <c r="P2" t="n">
-        <v>320.7934303901239</v>
+        <v>320.8296444919187</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -32313,28 +32417,28 @@
         <v>0.0512</v>
       </c>
       <c r="I3" t="n">
-        <v>0.06835062243817934</v>
+        <v>0.06425599547241161</v>
       </c>
       <c r="J3" t="n">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="K3" t="n">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01690846126181733</v>
+        <v>0.01496804406348107</v>
       </c>
       <c r="M3" t="n">
-        <v>3.083482735793852</v>
+        <v>3.090694621188941</v>
       </c>
       <c r="N3" t="n">
-        <v>14.61200466388011</v>
+        <v>14.68111155286446</v>
       </c>
       <c r="O3" t="n">
-        <v>3.822565194196184</v>
+        <v>3.831593865855887</v>
       </c>
       <c r="P3" t="n">
-        <v>318.0813062448228</v>
+        <v>318.1233363589773</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -32395,28 +32499,28 @@
         <v>0.046</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.03830545195475565</v>
+        <v>-0.04206115261230732</v>
       </c>
       <c r="J4" t="n">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="K4" t="n">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="L4" t="n">
-        <v>0.005880392524407974</v>
+        <v>0.007083533058211855</v>
       </c>
       <c r="M4" t="n">
-        <v>2.959883606300827</v>
+        <v>2.968152169786234</v>
       </c>
       <c r="N4" t="n">
-        <v>13.34407540984021</v>
+        <v>13.39897222080219</v>
       </c>
       <c r="O4" t="n">
-        <v>3.652954339961042</v>
+        <v>3.660460656912213</v>
       </c>
       <c r="P4" t="n">
-        <v>330.542810621975</v>
+        <v>330.5813617142049</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -32477,28 +32581,28 @@
         <v>0.0417</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.07718591770811241</v>
+        <v>-0.08157225980054465</v>
       </c>
       <c r="J5" t="n">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="K5" t="n">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02185451082328749</v>
+        <v>0.02430582572187001</v>
       </c>
       <c r="M5" t="n">
-        <v>2.828548737039652</v>
+        <v>2.838579916733187</v>
       </c>
       <c r="N5" t="n">
-        <v>14.34410625977964</v>
+        <v>14.43227113137169</v>
       </c>
       <c r="O5" t="n">
-        <v>3.787361384893134</v>
+        <v>3.798982907486119</v>
       </c>
       <c r="P5" t="n">
-        <v>340.9471873984322</v>
+        <v>340.9922117605717</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -32559,28 +32663,28 @@
         <v>0.0408</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.05649887203374512</v>
+        <v>-0.05895682550292777</v>
       </c>
       <c r="J6" t="n">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="K6" t="n">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01269014771187771</v>
+        <v>0.01386439717997889</v>
       </c>
       <c r="M6" t="n">
-        <v>2.867974221946995</v>
+        <v>2.87047842518409</v>
       </c>
       <c r="N6" t="n">
-        <v>13.3598422953648</v>
+        <v>13.35826912611337</v>
       </c>
       <c r="O6" t="n">
-        <v>3.655111803401477</v>
+        <v>3.654896595816819</v>
       </c>
       <c r="P6" t="n">
-        <v>341.3258670811438</v>
+        <v>341.3510971728161</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -32641,28 +32745,28 @@
         <v>0.0371</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.05879767717752677</v>
+        <v>-0.06181122790369398</v>
       </c>
       <c r="J7" t="n">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="K7" t="n">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0131091287077949</v>
+        <v>0.01451129736828249</v>
       </c>
       <c r="M7" t="n">
-        <v>2.877898944469566</v>
+        <v>2.88604467309054</v>
       </c>
       <c r="N7" t="n">
-        <v>14.006805334747</v>
+        <v>14.02524498064512</v>
       </c>
       <c r="O7" t="n">
-        <v>3.742566677394939</v>
+        <v>3.745029369797402</v>
       </c>
       <c r="P7" t="n">
-        <v>342.3115822069104</v>
+        <v>342.3425269900541</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -32723,28 +32827,28 @@
         <v>0.0403</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.01750782029777415</v>
+        <v>-0.01772226149925761</v>
       </c>
       <c r="J8" t="n">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="K8" t="n">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001693427032180339</v>
+        <v>0.001748401821286438</v>
       </c>
       <c r="M8" t="n">
-        <v>2.367589242412486</v>
+        <v>2.360731551688406</v>
       </c>
       <c r="N8" t="n">
-        <v>9.72067864673655</v>
+        <v>9.689099240605776</v>
       </c>
       <c r="O8" t="n">
-        <v>3.117800289745408</v>
+        <v>3.112731797088496</v>
       </c>
       <c r="P8" t="n">
-        <v>344.5806631186687</v>
+        <v>344.5828642043103</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -32805,28 +32909,28 @@
         <v>0.046</v>
       </c>
       <c r="I9" t="n">
-        <v>0.02734318302650347</v>
+        <v>0.02621057006300195</v>
       </c>
       <c r="J9" t="n">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="K9" t="n">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="L9" t="n">
-        <v>0.003428482494222673</v>
+        <v>0.003173022823785621</v>
       </c>
       <c r="M9" t="n">
-        <v>2.588930552903606</v>
+        <v>2.585064610285555</v>
       </c>
       <c r="N9" t="n">
-        <v>11.69067686050212</v>
+        <v>11.66127076573352</v>
       </c>
       <c r="O9" t="n">
-        <v>3.419163181321144</v>
+        <v>3.414860284950691</v>
       </c>
       <c r="P9" t="n">
-        <v>347.61944915327</v>
+        <v>347.6310750110643</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -32887,28 +32991,28 @@
         <v>0.0509</v>
       </c>
       <c r="I10" t="n">
-        <v>0.04194828817807142</v>
+        <v>0.04121225887068948</v>
       </c>
       <c r="J10" t="n">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="K10" t="n">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="L10" t="n">
-        <v>0.007886819030028858</v>
+        <v>0.007670552993388369</v>
       </c>
       <c r="M10" t="n">
-        <v>2.772207300613313</v>
+        <v>2.767482290853716</v>
       </c>
       <c r="N10" t="n">
-        <v>11.90756093878165</v>
+        <v>11.8721233982053</v>
       </c>
       <c r="O10" t="n">
-        <v>3.450733391437485</v>
+        <v>3.445594781486253</v>
       </c>
       <c r="P10" t="n">
-        <v>341.111252912622</v>
+        <v>341.1188079896444</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -32969,28 +33073,28 @@
         <v>0.0522</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.008998863497693204</v>
+        <v>-0.009842290540537068</v>
       </c>
       <c r="J11" t="n">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="K11" t="n">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0003363706559925683</v>
+        <v>0.0004053006952285942</v>
       </c>
       <c r="M11" t="n">
-        <v>2.911579781512275</v>
+        <v>2.906065672954666</v>
       </c>
       <c r="N11" t="n">
-        <v>12.94631294052428</v>
+        <v>12.90878350521771</v>
       </c>
       <c r="O11" t="n">
-        <v>3.598098517345555</v>
+        <v>3.59287955618021</v>
       </c>
       <c r="P11" t="n">
-        <v>333.4274908000678</v>
+        <v>333.4361482409633</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -33032,7 +33136,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L605"/>
+  <dimension ref="A1:L607"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70541,6 +70645,130 @@
         </is>
       </c>
     </row>
+    <row r="606">
+      <c r="A606" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:12:09+00:00</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>-36.60177558200247,174.7083272939501</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>-36.60244860395561,174.70865108662548</t>
+        </is>
+      </c>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>-36.60308878395378,174.7090987645097</t>
+        </is>
+      </c>
+      <c r="E606" t="inlineStr">
+        <is>
+          <t>-36.603725201516475,174.70957381608662</t>
+        </is>
+      </c>
+      <c r="F606" t="inlineStr">
+        <is>
+          <t>-36.604340193144274,174.7100696515918</t>
+        </is>
+      </c>
+      <c r="G606" t="inlineStr">
+        <is>
+          <t>-36.60496516751634,174.71051862330924</t>
+        </is>
+      </c>
+      <c r="H606" t="inlineStr">
+        <is>
+          <t>-36.605552279851366,174.71104671201624</t>
+        </is>
+      </c>
+      <c r="I606" t="inlineStr">
+        <is>
+          <t>-36.606167145947275,174.71153390357364</t>
+        </is>
+      </c>
+      <c r="J606" t="inlineStr">
+        <is>
+          <t>-36.606779191636825,174.71203190611024</t>
+        </is>
+      </c>
+      <c r="K606" t="inlineStr">
+        <is>
+          <t>-36.607403512791336,174.71249784954307</t>
+        </is>
+      </c>
+      <c r="L606" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:06:18+00:00</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>-36.60177120505162,174.70834016842477</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>-36.60244671310281,174.7086566484409</t>
+        </is>
+      </c>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>-36.60308610956076,174.7091060972745</t>
+        </is>
+      </c>
+      <c r="E607" t="inlineStr">
+        <is>
+          <t>-36.603720205863965,174.70958533346342</t>
+        </is>
+      </c>
+      <c r="F607" t="inlineStr">
+        <is>
+          <t>-36.60433729152962,174.71007570474782</t>
+        </is>
+      </c>
+      <c r="G607" t="inlineStr">
+        <is>
+          <t>-36.60495948995644,174.71053043223458</t>
+        </is>
+      </c>
+      <c r="H607" t="inlineStr">
+        <is>
+          <t>-36.60555010024315,174.71105121688367</t>
+        </is>
+      </c>
+      <c r="I607" t="inlineStr">
+        <is>
+          <t>-36.60616450258647,174.71153870342064</t>
+        </is>
+      </c>
+      <c r="J607" t="inlineStr">
+        <is>
+          <t>-36.60677747623789,174.71203464132805</t>
+        </is>
+      </c>
+      <c r="K607" t="inlineStr">
+        <is>
+          <t>-36.60740056309003,174.71250250951599</t>
+        </is>
+      </c>
+      <c r="L607" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0141/nzd0141.xlsx
+++ b/data/nzd0141/nzd0141.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L607"/>
+  <dimension ref="A1:L608"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25938,6 +25938,48 @@
         <v>332.22</v>
       </c>
       <c r="L607" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:06:08+00:00</t>
+        </is>
+      </c>
+      <c r="B608" t="n">
+        <v>316.3</v>
+      </c>
+      <c r="C608" t="n">
+        <v>314.46</v>
+      </c>
+      <c r="D608" t="n">
+        <v>324.47</v>
+      </c>
+      <c r="E608" t="n">
+        <v>333.3</v>
+      </c>
+      <c r="F608" t="n">
+        <v>334</v>
+      </c>
+      <c r="G608" t="n">
+        <v>335.82</v>
+      </c>
+      <c r="H608" t="n">
+        <v>342.19</v>
+      </c>
+      <c r="I608" t="n">
+        <v>345.44</v>
+      </c>
+      <c r="J608" t="n">
+        <v>339.18</v>
+      </c>
+      <c r="K608" t="n">
+        <v>330.81</v>
+      </c>
+      <c r="L608" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -25954,7 +25996,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B621"/>
+  <dimension ref="A1:B622"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32167,6 +32209,16 @@
       </c>
       <c r="B621" t="n">
         <v>1.4</v>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B622" t="n">
+        <v>0.54</v>
       </c>
     </row>
   </sheetData>
@@ -32335,28 +32387,28 @@
         <v>0.0356</v>
       </c>
       <c r="I2" t="n">
-        <v>0.003061211719461946</v>
+        <v>0.001480526060056365</v>
       </c>
       <c r="J2" t="n">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="K2" t="n">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="L2" t="n">
-        <v>2.998888405980615e-05</v>
+        <v>7.027491365163563e-06</v>
       </c>
       <c r="M2" t="n">
-        <v>3.145885400345232</v>
+        <v>3.147251280019021</v>
       </c>
       <c r="N2" t="n">
-        <v>16.8833943507199</v>
+        <v>16.89044571397415</v>
       </c>
       <c r="O2" t="n">
-        <v>4.108940782089698</v>
+        <v>4.109798743731152</v>
       </c>
       <c r="P2" t="n">
-        <v>320.8296444919187</v>
+        <v>320.8459299814</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -32417,28 +32469,28 @@
         <v>0.0512</v>
       </c>
       <c r="I3" t="n">
-        <v>0.06425599547241161</v>
+        <v>0.06242100413360719</v>
       </c>
       <c r="J3" t="n">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="K3" t="n">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01496804406348107</v>
+        <v>0.01414663971505492</v>
       </c>
       <c r="M3" t="n">
-        <v>3.090694621188941</v>
+        <v>3.093422698177673</v>
       </c>
       <c r="N3" t="n">
-        <v>14.68111155286446</v>
+        <v>14.70391216105668</v>
       </c>
       <c r="O3" t="n">
-        <v>3.831593865855887</v>
+        <v>3.834568054039031</v>
       </c>
       <c r="P3" t="n">
-        <v>318.1233363589773</v>
+        <v>318.1422419092166</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -32499,28 +32551,28 @@
         <v>0.046</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.04206115261230732</v>
+        <v>-0.04377635682516052</v>
       </c>
       <c r="J4" t="n">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="K4" t="n">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="L4" t="n">
-        <v>0.007083533058211855</v>
+        <v>0.00767466605207745</v>
       </c>
       <c r="M4" t="n">
-        <v>2.968152169786234</v>
+        <v>2.97148396311059</v>
       </c>
       <c r="N4" t="n">
-        <v>13.39897222080219</v>
+        <v>13.41795075521416</v>
       </c>
       <c r="O4" t="n">
-        <v>3.660460656912213</v>
+        <v>3.663052109268193</v>
       </c>
       <c r="P4" t="n">
-        <v>330.5813617142049</v>
+        <v>330.5990331215468</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -32581,28 +32633,28 @@
         <v>0.0417</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.08157225980054465</v>
+        <v>-0.08347177124172911</v>
       </c>
       <c r="J5" t="n">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="K5" t="n">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02430582572187001</v>
+        <v>0.02543141156327267</v>
       </c>
       <c r="M5" t="n">
-        <v>2.838579916733187</v>
+        <v>2.842315924437329</v>
       </c>
       <c r="N5" t="n">
-        <v>14.43227113137169</v>
+        <v>14.45884399566332</v>
       </c>
       <c r="O5" t="n">
-        <v>3.798982907486119</v>
+        <v>3.802478664721647</v>
       </c>
       <c r="P5" t="n">
-        <v>340.9922117605717</v>
+        <v>341.0117820485736</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -32663,28 +32715,28 @@
         <v>0.0408</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.05895682550292777</v>
+        <v>-0.06094195991091225</v>
       </c>
       <c r="J6" t="n">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="K6" t="n">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01386439717997889</v>
+        <v>0.01479619604219573</v>
       </c>
       <c r="M6" t="n">
-        <v>2.87047842518409</v>
+        <v>2.875366368787688</v>
       </c>
       <c r="N6" t="n">
-        <v>13.35826912611337</v>
+        <v>13.39125277209802</v>
       </c>
       <c r="O6" t="n">
-        <v>3.654896595816819</v>
+        <v>3.659406068216265</v>
       </c>
       <c r="P6" t="n">
-        <v>341.3510971728161</v>
+        <v>341.3715496171893</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -32745,28 +32797,28 @@
         <v>0.0371</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.06181122790369398</v>
+        <v>-0.06348871623949302</v>
       </c>
       <c r="J7" t="n">
+        <v>607</v>
+      </c>
+      <c r="K7" t="n">
         <v>606</v>
       </c>
-      <c r="K7" t="n">
-        <v>605</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.01451129736828249</v>
+        <v>0.01531349954071348</v>
       </c>
       <c r="M7" t="n">
-        <v>2.88604467309054</v>
+        <v>2.891025596791855</v>
       </c>
       <c r="N7" t="n">
-        <v>14.02524498064512</v>
+        <v>14.04140931156134</v>
       </c>
       <c r="O7" t="n">
-        <v>3.745029369797402</v>
+        <v>3.7471868530354</v>
       </c>
       <c r="P7" t="n">
-        <v>342.3425269900541</v>
+        <v>342.3598165108052</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -32827,28 +32879,28 @@
         <v>0.0403</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.01772226149925761</v>
+        <v>-0.01838233451291216</v>
       </c>
       <c r="J8" t="n">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="K8" t="n">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001748401821286438</v>
+        <v>0.001886918876352062</v>
       </c>
       <c r="M8" t="n">
-        <v>2.360731551688406</v>
+        <v>2.359756611617399</v>
       </c>
       <c r="N8" t="n">
-        <v>9.689099240605776</v>
+        <v>9.679216823135626</v>
       </c>
       <c r="O8" t="n">
-        <v>3.112731797088496</v>
+        <v>3.111143973385935</v>
       </c>
       <c r="P8" t="n">
-        <v>344.5828642043103</v>
+        <v>344.5896648050855</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -32909,28 +32961,28 @@
         <v>0.046</v>
       </c>
       <c r="I9" t="n">
-        <v>0.02621057006300195</v>
+        <v>0.02522137421285132</v>
       </c>
       <c r="J9" t="n">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="K9" t="n">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="L9" t="n">
-        <v>0.003173022823785621</v>
+        <v>0.002946655595325476</v>
       </c>
       <c r="M9" t="n">
-        <v>2.585064610285555</v>
+        <v>2.584872342170996</v>
       </c>
       <c r="N9" t="n">
-        <v>11.66127076573352</v>
+        <v>11.65571388423306</v>
       </c>
       <c r="O9" t="n">
-        <v>3.414860284950691</v>
+        <v>3.414046555662804</v>
       </c>
       <c r="P9" t="n">
-        <v>347.6310750110643</v>
+        <v>347.6412664988637</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -32991,28 +33043,28 @@
         <v>0.0509</v>
       </c>
       <c r="I10" t="n">
-        <v>0.04121225887068948</v>
+        <v>0.04017424410641507</v>
       </c>
       <c r="J10" t="n">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="K10" t="n">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="L10" t="n">
-        <v>0.007670552993388369</v>
+        <v>0.007310687818140371</v>
       </c>
       <c r="M10" t="n">
-        <v>2.767482290853716</v>
+        <v>2.769154412909114</v>
       </c>
       <c r="N10" t="n">
-        <v>11.8721233982053</v>
+        <v>11.86760015641476</v>
       </c>
       <c r="O10" t="n">
-        <v>3.445594781486253</v>
+        <v>3.444938338550454</v>
       </c>
       <c r="P10" t="n">
-        <v>341.1188079896444</v>
+        <v>341.1295024489916</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -33073,28 +33125,28 @@
         <v>0.0522</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.009842290540537068</v>
+        <v>-0.01065444419209533</v>
       </c>
       <c r="J11" t="n">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="K11" t="n">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0004053006952285942</v>
+        <v>0.0004764174970041113</v>
       </c>
       <c r="M11" t="n">
-        <v>2.906065672954666</v>
+        <v>2.905182613173826</v>
       </c>
       <c r="N11" t="n">
-        <v>12.90878350521771</v>
+        <v>12.89672116718302</v>
       </c>
       <c r="O11" t="n">
-        <v>3.59287955618021</v>
+        <v>3.591200518932774</v>
       </c>
       <c r="P11" t="n">
-        <v>333.4361482409633</v>
+        <v>333.4445156982569</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -33136,7 +33188,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L607"/>
+  <dimension ref="A1:L608"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70769,6 +70821,68 @@
         </is>
       </c>
     </row>
+    <row r="608">
+      <c r="A608" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:06:08+00:00</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>-36.60177166025456,174.70833882947946</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>-36.60244566262891,174.70865973833824</t>
+        </is>
+      </c>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>-36.603085849550304,174.7091068101822</t>
+        </is>
+      </c>
+      <c r="E608" t="inlineStr">
+        <is>
+          <t>-36.60371930920828,174.70958740068474</t>
+        </is>
+      </c>
+      <c r="F608" t="inlineStr">
+        <is>
+          <t>-36.60434908221589,174.71005110779353</t>
+        </is>
+      </c>
+      <c r="G608" t="inlineStr">
+        <is>
+          <t>-36.604964798244175,174.71051939136947</t>
+        </is>
+      </c>
+      <c r="H608" t="inlineStr">
+        <is>
+          <t>-36.60555867955114,174.71103348495714</t>
+        </is>
+      </c>
+      <c r="I608" t="inlineStr">
+        <is>
+          <t>-36.60617212766519,174.71152485770725</t>
+        </is>
+      </c>
+      <c r="J608" t="inlineStr">
+        <is>
+          <t>-36.6067891520166,174.71201602419816</t>
+        </is>
+      </c>
+      <c r="K608" t="inlineStr">
+        <is>
+          <t>-36.60740841040819,174.71249011222875</t>
+        </is>
+      </c>
+      <c r="L608" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0141/nzd0141.xlsx
+++ b/data/nzd0141/nzd0141.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L608"/>
+  <dimension ref="A1:L610"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25980,6 +25980,90 @@
         <v>330.81</v>
       </c>
       <c r="L608" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-01 22:11:52+00:00</t>
+        </is>
+      </c>
+      <c r="B609" t="n">
+        <v>316.23</v>
+      </c>
+      <c r="C609" t="n">
+        <v>312.66</v>
+      </c>
+      <c r="D609" t="n">
+        <v>323.28</v>
+      </c>
+      <c r="E609" t="n">
+        <v>333.38</v>
+      </c>
+      <c r="F609" t="n">
+        <v>335.05</v>
+      </c>
+      <c r="G609" t="n">
+        <v>337.36</v>
+      </c>
+      <c r="H609" t="n">
+        <v>341.74</v>
+      </c>
+      <c r="I609" t="n">
+        <v>345.19</v>
+      </c>
+      <c r="J609" t="n">
+        <v>338.58</v>
+      </c>
+      <c r="K609" t="n">
+        <v>325.42</v>
+      </c>
+      <c r="L609" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:05:38+00:00</t>
+        </is>
+      </c>
+      <c r="B610" t="n">
+        <v>317.82</v>
+      </c>
+      <c r="C610" t="n">
+        <v>313.72</v>
+      </c>
+      <c r="D610" t="n">
+        <v>324.09</v>
+      </c>
+      <c r="E610" t="n">
+        <v>334.72</v>
+      </c>
+      <c r="F610" t="n">
+        <v>336.19</v>
+      </c>
+      <c r="G610" t="n">
+        <v>338.83</v>
+      </c>
+      <c r="H610" t="n">
+        <v>342.11</v>
+      </c>
+      <c r="I610" t="n">
+        <v>345.72</v>
+      </c>
+      <c r="J610" t="n">
+        <v>339.4</v>
+      </c>
+      <c r="K610" t="n">
+        <v>325.32</v>
+      </c>
+      <c r="L610" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -25996,7 +26080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B622"/>
+  <dimension ref="A1:B624"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32219,6 +32303,26 @@
       </c>
       <c r="B622" t="n">
         <v>0.54</v>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>2026-02-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B623" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B624" t="n">
+        <v>-0.21</v>
       </c>
     </row>
   </sheetData>
@@ -32387,34 +32491,30 @@
         <v>0.0356</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001480526060056365</v>
+        <v>-0.001152613034059111</v>
       </c>
       <c r="J2" t="n">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="K2" t="n">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="L2" t="n">
-        <v>7.027491365163563e-06</v>
+        <v>4.279659215788989e-06</v>
       </c>
       <c r="M2" t="n">
-        <v>3.147251280019021</v>
+        <v>3.147788590147096</v>
       </c>
       <c r="N2" t="n">
-        <v>16.89044571397415</v>
+        <v>16.88544755236957</v>
       </c>
       <c r="O2" t="n">
-        <v>4.109798743731152</v>
+        <v>4.109190620106297</v>
       </c>
       <c r="P2" t="n">
-        <v>320.8459299814</v>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>320.8731399102844</v>
+      </c>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
         <is>
           <t>LINESTRING (174.70508102449966 -36.60287916059808, 174.71456917176945 -36.59965330419953)</t>
@@ -32469,34 +32569,30 @@
         <v>0.0512</v>
       </c>
       <c r="I3" t="n">
-        <v>0.06242100413360719</v>
+        <v>0.0579147575910816</v>
       </c>
       <c r="J3" t="n">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="K3" t="n">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01414663971505492</v>
+        <v>0.01217876689205843</v>
       </c>
       <c r="M3" t="n">
-        <v>3.093422698177673</v>
+        <v>3.102482717741124</v>
       </c>
       <c r="N3" t="n">
-        <v>14.70391216105668</v>
+        <v>14.79824096754108</v>
       </c>
       <c r="O3" t="n">
-        <v>3.834568054039031</v>
+        <v>3.846848186183213</v>
       </c>
       <c r="P3" t="n">
-        <v>318.1422419092166</v>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>318.1888108469544</v>
+      </c>
+      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
         <is>
           <t>LINESTRING (174.70542086049136 -36.60354672647075, 174.7149090500694 -36.600320861020606)</t>
@@ -32551,34 +32647,30 @@
         <v>0.046</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.04377635682516052</v>
+        <v>-0.04770263747907411</v>
       </c>
       <c r="J4" t="n">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="K4" t="n">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00767466605207745</v>
+        <v>0.009097410686494833</v>
       </c>
       <c r="M4" t="n">
-        <v>2.97148396311059</v>
+        <v>2.980735239209972</v>
       </c>
       <c r="N4" t="n">
-        <v>13.41795075521416</v>
+        <v>13.48200600810222</v>
       </c>
       <c r="O4" t="n">
-        <v>3.663052109268193</v>
+        <v>3.671785125535292</v>
       </c>
       <c r="P4" t="n">
-        <v>330.5990331215468</v>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>330.6396086970238</v>
+      </c>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
         <is>
           <t>LINESTRING (174.70580222658228 -36.6042910276972, 174.71518394350093 -36.600869191780774)</t>
@@ -32633,34 +32725,30 @@
         <v>0.0417</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.08347177124172911</v>
+        <v>-0.0867153674782269</v>
       </c>
       <c r="J5" t="n">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="K5" t="n">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02543141156327267</v>
+        <v>0.02745994680911545</v>
       </c>
       <c r="M5" t="n">
-        <v>2.842315924437329</v>
+        <v>2.847649070040003</v>
       </c>
       <c r="N5" t="n">
-        <v>14.45884399566332</v>
+        <v>14.48626789845251</v>
       </c>
       <c r="O5" t="n">
-        <v>3.802478664721647</v>
+        <v>3.806083012554049</v>
       </c>
       <c r="P5" t="n">
-        <v>341.0117820485736</v>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>341.0453013272563</v>
+      </c>
+      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
           <t>LINESTRING (174.70630636358473 -36.60514238613091, 174.7153736554813 -36.6012093062123)</t>
@@ -32715,34 +32803,30 @@
         <v>0.0408</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.06094195991091225</v>
+        <v>-0.06376561592575693</v>
       </c>
       <c r="J6" t="n">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="K6" t="n">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01479619604219573</v>
+        <v>0.01623260745209587</v>
       </c>
       <c r="M6" t="n">
-        <v>2.875366368787688</v>
+        <v>2.879558637501685</v>
       </c>
       <c r="N6" t="n">
-        <v>13.39125277209802</v>
+        <v>13.40398166641379</v>
       </c>
       <c r="O6" t="n">
-        <v>3.659406068216265</v>
+        <v>3.661144857338179</v>
       </c>
       <c r="P6" t="n">
-        <v>341.3715496171893</v>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>341.4007292960658</v>
+      </c>
+      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
         <is>
           <t>LINESTRING (174.70684190853217 -36.605887356235456, 174.7156915527065 -36.60164507960872)</t>
@@ -32797,34 +32881,30 @@
         <v>0.0371</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.06348871623949302</v>
+        <v>-0.06525541628833241</v>
       </c>
       <c r="J7" t="n">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="K7" t="n">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01531349954071348</v>
+        <v>0.01626056273198462</v>
       </c>
       <c r="M7" t="n">
-        <v>2.891025596791855</v>
+        <v>2.891702741616534</v>
       </c>
       <c r="N7" t="n">
-        <v>14.04140931156134</v>
+        <v>14.01882005900638</v>
       </c>
       <c r="O7" t="n">
-        <v>3.7471868530354</v>
+        <v>3.744171478312175</v>
       </c>
       <c r="P7" t="n">
-        <v>342.3598165108052</v>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>342.3780794058299</v>
+      </c>
+      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
         <is>
           <t>LINESTRING (174.7072952008347 -36.60651486829019, 174.71613795994745 -36.60226324855399)</t>
@@ -32879,34 +32959,30 @@
         <v>0.0403</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.01838233451291216</v>
+        <v>-0.01986856349144184</v>
       </c>
       <c r="J8" t="n">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="K8" t="n">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001886918876352062</v>
+        <v>0.00221725453398447</v>
       </c>
       <c r="M8" t="n">
-        <v>2.359756611617399</v>
+        <v>2.358500781472359</v>
       </c>
       <c r="N8" t="n">
-        <v>9.679216823135626</v>
+        <v>9.66295472793556</v>
       </c>
       <c r="O8" t="n">
-        <v>3.111143973385935</v>
+        <v>3.108529351306749</v>
       </c>
       <c r="P8" t="n">
-        <v>344.5896648050855</v>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>344.6050239179699</v>
+      </c>
+      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
         <is>
           <t>LINESTRING (174.7077535848802 -36.60714552943492, 174.7165816240392 -36.602874082777355)</t>
@@ -32961,34 +33037,30 @@
         <v>0.046</v>
       </c>
       <c r="I9" t="n">
-        <v>0.02522137421285132</v>
+        <v>0.02327474026699366</v>
       </c>
       <c r="J9" t="n">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="K9" t="n">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="L9" t="n">
-        <v>0.002946655595325476</v>
+        <v>0.002524190852619679</v>
       </c>
       <c r="M9" t="n">
-        <v>2.584872342170996</v>
+        <v>2.584300894883479</v>
       </c>
       <c r="N9" t="n">
-        <v>11.65571388423306</v>
+        <v>11.64411376087742</v>
       </c>
       <c r="O9" t="n">
-        <v>3.414046555662804</v>
+        <v>3.412347250922365</v>
       </c>
       <c r="P9" t="n">
-        <v>347.6412664988637</v>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>347.6613834737236</v>
+      </c>
+      <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
         <is>
           <t>LINESTRING (174.7083362086651 -36.60792809124111, 174.7168371638177 -36.60324632165825)</t>
@@ -33043,34 +33115,30 @@
         <v>0.0509</v>
       </c>
       <c r="I10" t="n">
-        <v>0.04017424410641507</v>
+        <v>0.03798807439081106</v>
       </c>
       <c r="J10" t="n">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="K10" t="n">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="L10" t="n">
-        <v>0.007310687818140371</v>
+        <v>0.006573696724540667</v>
       </c>
       <c r="M10" t="n">
-        <v>2.769154412909114</v>
+        <v>2.773071704942438</v>
       </c>
       <c r="N10" t="n">
-        <v>11.86760015641476</v>
+        <v>11.86252443972634</v>
       </c>
       <c r="O10" t="n">
-        <v>3.444938338550454</v>
+        <v>3.444201567813118</v>
       </c>
       <c r="P10" t="n">
-        <v>341.1295024489916</v>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>341.1520944601907</v>
+      </c>
+      <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
         <is>
           <t>LINESTRING (174.70902326902805 -36.60866598339965, 174.71714845744918 -36.60357009400172)</t>
@@ -33125,34 +33193,30 @@
         <v>0.0522</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.01065444419209533</v>
+        <v>-0.01597143892032501</v>
       </c>
       <c r="J11" t="n">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="K11" t="n">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0004764174970041113</v>
+        <v>0.001061986428943618</v>
       </c>
       <c r="M11" t="n">
-        <v>2.905182613173826</v>
+        <v>2.921193314820654</v>
       </c>
       <c r="N11" t="n">
-        <v>12.89672116718302</v>
+        <v>13.05161435765462</v>
       </c>
       <c r="O11" t="n">
-        <v>3.591200518932774</v>
+        <v>3.612701808571338</v>
       </c>
       <c r="P11" t="n">
-        <v>333.4445156982569</v>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>333.4994655846206</v>
+      </c>
+      <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
           <t>LINESTRING (174.70958142760406 -36.60924949069242, 174.71767809278495 -36.60412423971357)</t>
@@ -33188,7 +33252,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L608"/>
+  <dimension ref="A1:L610"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -70883,6 +70947,130 @@
         </is>
       </c>
     </row>
+    <row r="609">
+      <c r="A609" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-01 22:11:52+00:00</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>-36.601771905363854,174.7083381085089</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>-36.60245196547109,174.70864119895296</t>
+        </is>
+      </c>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>-36.60309026972751,174.70909469075121</t>
+        </is>
+      </c>
+      <c r="E609" t="inlineStr">
+        <is>
+          <t>-36.603718967625156,174.7095881881976</t>
+        </is>
+      </c>
+      <c r="F609" t="inlineStr">
+        <is>
+          <t>-36.604344246192824,174.71006119638898</t>
+        </is>
+      </c>
+      <c r="G609" t="inlineStr">
+        <is>
+          <t>-36.60495768975429,174.71053417652763</t>
+        </is>
+      </c>
+      <c r="H609" t="inlineStr">
+        <is>
+          <t>-36.60556076640943,174.7110291717852</t>
+        </is>
+      </c>
+      <c r="I609" t="inlineStr">
+        <is>
+          <t>-36.6061733985115,174.7115225500881</t>
+        </is>
+      </c>
+      <c r="J609" t="inlineStr">
+        <is>
+          <t>-36.606792472142736,174.71201073022655</t>
+        </is>
+      </c>
+      <c r="K609" t="inlineStr">
+        <is>
+          <t>-36.60743840830098,174.71244272115698</t>
+        </is>
+      </c>
+      <c r="L609" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:05:38+00:00</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>-36.60176633788068,174.70835448483882</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>-36.60244825379771,174.70865211659134</t>
+        </is>
+      </c>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>-36.6030872610356,174.70910294011196</t>
+        </is>
+      </c>
+      <c r="E610" t="inlineStr">
+        <is>
+          <t>-36.60371324610698,174.7096013790371</t>
+        </is>
+      </c>
+      <c r="F610" t="inlineStr">
+        <is>
+          <t>-36.604338995652554,174.71007214971976</t>
+        </is>
+      </c>
+      <c r="G610" t="inlineStr">
+        <is>
+          <t>-36.60495090437593,174.71054828963057</t>
+        </is>
+      </c>
+      <c r="H610" t="inlineStr">
+        <is>
+          <t>-36.60555905054817,174.71103271817103</t>
+        </is>
+      </c>
+      <c r="I610" t="inlineStr">
+        <is>
+          <t>-36.606170704317286,174.71152744224062</t>
+        </is>
+      </c>
+      <c r="J610" t="inlineStr">
+        <is>
+          <t>-36.606787934636955,174.71201796532097</t>
+        </is>
+      </c>
+      <c r="K610" t="inlineStr">
+        <is>
+          <t>-36.60743896484799,174.71244184191596</t>
+        </is>
+      </c>
+      <c r="L610" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0141/nzd0141.xlsx
+++ b/data/nzd0141/nzd0141.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L610"/>
+  <dimension ref="A1:L611"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26066,6 +26066,48 @@
       <c r="L610" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:05:33+00:00</t>
+        </is>
+      </c>
+      <c r="B611" t="n">
+        <v>319.78</v>
+      </c>
+      <c r="C611" t="n">
+        <v>314.14</v>
+      </c>
+      <c r="D611" t="n">
+        <v>324.9</v>
+      </c>
+      <c r="E611" t="n">
+        <v>337.4</v>
+      </c>
+      <c r="F611" t="n">
+        <v>339.15</v>
+      </c>
+      <c r="G611" t="n">
+        <v>341.59</v>
+      </c>
+      <c r="H611" t="n">
+        <v>342.32</v>
+      </c>
+      <c r="I611" t="n">
+        <v>345.42</v>
+      </c>
+      <c r="J611" t="n">
+        <v>339.31</v>
+      </c>
+      <c r="K611" t="n">
+        <v>330.19</v>
+      </c>
+      <c r="L611" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -26080,7 +26122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B624"/>
+  <dimension ref="A1:B625"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32323,6 +32365,16 @@
       </c>
       <c r="B624" t="n">
         <v>-0.21</v>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B625" t="n">
+        <v>1.24</v>
       </c>
     </row>
   </sheetData>
@@ -32491,28 +32543,28 @@
         <v>0.0356</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.001152613034059111</v>
+        <v>-0.001516391447090328</v>
       </c>
       <c r="J2" t="n">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="K2" t="n">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="L2" t="n">
-        <v>4.279659215788989e-06</v>
+        <v>7.435679243994464e-06</v>
       </c>
       <c r="M2" t="n">
-        <v>3.147788590147096</v>
+        <v>3.144117603987338</v>
       </c>
       <c r="N2" t="n">
-        <v>16.88544755236957</v>
+        <v>16.85960116485345</v>
       </c>
       <c r="O2" t="n">
-        <v>4.109190620106297</v>
+        <v>4.10604446698443</v>
       </c>
       <c r="P2" t="n">
-        <v>320.8731399102844</v>
+        <v>320.8769181364937</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -32569,28 +32621,28 @@
         <v>0.0512</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0579147575910816</v>
+        <v>0.05599924931671564</v>
       </c>
       <c r="J3" t="n">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="K3" t="n">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01217876689205843</v>
+        <v>0.01140099554672536</v>
       </c>
       <c r="M3" t="n">
-        <v>3.102482717741124</v>
+        <v>3.105586301342266</v>
       </c>
       <c r="N3" t="n">
-        <v>14.79824096754108</v>
+        <v>14.82485054832928</v>
       </c>
       <c r="O3" t="n">
-        <v>3.846848186183213</v>
+        <v>3.850305253915497</v>
       </c>
       <c r="P3" t="n">
-        <v>318.1888108469544</v>
+        <v>318.2087054402212</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -32647,28 +32699,28 @@
         <v>0.046</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.04770263747907411</v>
+        <v>-0.0492367537560138</v>
       </c>
       <c r="J4" t="n">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="K4" t="n">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="L4" t="n">
-        <v>0.009097410686494833</v>
+        <v>0.009700639095986729</v>
       </c>
       <c r="M4" t="n">
-        <v>2.980735239209972</v>
+        <v>2.983185463726829</v>
       </c>
       <c r="N4" t="n">
-        <v>13.48200600810222</v>
+        <v>13.49253319818491</v>
       </c>
       <c r="O4" t="n">
-        <v>3.671785125535292</v>
+        <v>3.673218370609745</v>
       </c>
       <c r="P4" t="n">
-        <v>330.6396086970238</v>
+        <v>330.6555421282503</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -32725,28 +32777,28 @@
         <v>0.0417</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0867153674782269</v>
+        <v>-0.08717528282496267</v>
       </c>
       <c r="J5" t="n">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="K5" t="n">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02745994680911545</v>
+        <v>0.02784447151011971</v>
       </c>
       <c r="M5" t="n">
-        <v>2.847649070040003</v>
+        <v>2.845040411912783</v>
       </c>
       <c r="N5" t="n">
-        <v>14.48626789845251</v>
+        <v>14.46545243754538</v>
       </c>
       <c r="O5" t="n">
-        <v>3.806083012554049</v>
+        <v>3.803347530471727</v>
       </c>
       <c r="P5" t="n">
-        <v>341.0453013272563</v>
+        <v>341.0500780378991</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -32803,28 +32855,28 @@
         <v>0.0408</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.06376561592575693</v>
+        <v>-0.06395527766545368</v>
       </c>
       <c r="J6" t="n">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="K6" t="n">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01623260745209587</v>
+        <v>0.01639029002041503</v>
       </c>
       <c r="M6" t="n">
-        <v>2.879558637501685</v>
+        <v>2.875755823013425</v>
       </c>
       <c r="N6" t="n">
-        <v>13.40398166641379</v>
+        <v>13.38250663190294</v>
       </c>
       <c r="O6" t="n">
-        <v>3.661144857338179</v>
+        <v>3.658210851208954</v>
       </c>
       <c r="P6" t="n">
-        <v>341.4007292960658</v>
+        <v>341.4026991352047</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -32881,28 +32933,28 @@
         <v>0.0371</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.06525541628833241</v>
+        <v>-0.06493235508386448</v>
       </c>
       <c r="J7" t="n">
+        <v>610</v>
+      </c>
+      <c r="K7" t="n">
         <v>609</v>
       </c>
-      <c r="K7" t="n">
-        <v>608</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.01626056273198462</v>
+        <v>0.0161631597968207</v>
       </c>
       <c r="M7" t="n">
-        <v>2.891702741616534</v>
+        <v>2.888181856714403</v>
       </c>
       <c r="N7" t="n">
-        <v>14.01882005900638</v>
+        <v>13.99724906807157</v>
       </c>
       <c r="O7" t="n">
-        <v>3.744171478312175</v>
+        <v>3.74128975997203</v>
       </c>
       <c r="P7" t="n">
-        <v>342.3780794058299</v>
+        <v>342.3747227212996</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -32959,28 +33011,28 @@
         <v>0.0403</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.01986856349144184</v>
+        <v>-0.02047041002375641</v>
       </c>
       <c r="J8" t="n">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="K8" t="n">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="L8" t="n">
-        <v>0.00221725453398447</v>
+        <v>0.002361301685909201</v>
       </c>
       <c r="M8" t="n">
-        <v>2.358500781472359</v>
+        <v>2.357228866807048</v>
       </c>
       <c r="N8" t="n">
-        <v>9.66295472793556</v>
+        <v>9.65213558595886</v>
       </c>
       <c r="O8" t="n">
-        <v>3.108529351306749</v>
+        <v>3.106788629108659</v>
       </c>
       <c r="P8" t="n">
-        <v>344.6050239179699</v>
+        <v>344.6112747351183</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -33037,28 +33089,28 @@
         <v>0.046</v>
       </c>
       <c r="I9" t="n">
-        <v>0.02327474026699366</v>
+        <v>0.02229270140600487</v>
       </c>
       <c r="J9" t="n">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="K9" t="n">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="L9" t="n">
-        <v>0.002524190852619679</v>
+        <v>0.002322581454335726</v>
       </c>
       <c r="M9" t="n">
-        <v>2.584300894883479</v>
+        <v>2.584009174523568</v>
       </c>
       <c r="N9" t="n">
-        <v>11.64411376087742</v>
+        <v>11.63839538873534</v>
       </c>
       <c r="O9" t="n">
-        <v>3.412347250922365</v>
+        <v>3.411509253795941</v>
       </c>
       <c r="P9" t="n">
-        <v>347.6613834737236</v>
+        <v>347.6715829930745</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -33115,28 +33167,28 @@
         <v>0.0509</v>
       </c>
       <c r="I10" t="n">
-        <v>0.03798807439081106</v>
+        <v>0.03700889656971363</v>
       </c>
       <c r="J10" t="n">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="K10" t="n">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="L10" t="n">
-        <v>0.006573696724540667</v>
+        <v>0.0062586748896033</v>
       </c>
       <c r="M10" t="n">
-        <v>2.773071704942438</v>
+        <v>2.774288962783998</v>
       </c>
       <c r="N10" t="n">
-        <v>11.86252443972634</v>
+        <v>11.85637022535846</v>
       </c>
       <c r="O10" t="n">
-        <v>3.444201567813118</v>
+        <v>3.443308035212427</v>
       </c>
       <c r="P10" t="n">
-        <v>341.1520944601907</v>
+        <v>341.1622642645957</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -33193,28 +33245,28 @@
         <v>0.0522</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.01597143892032501</v>
+        <v>-0.01695930468857033</v>
       </c>
       <c r="J11" t="n">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="K11" t="n">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="L11" t="n">
-        <v>0.001061986428943618</v>
+        <v>0.00120071638491015</v>
       </c>
       <c r="M11" t="n">
-        <v>2.921193314820654</v>
+        <v>2.921143686340968</v>
       </c>
       <c r="N11" t="n">
-        <v>13.05161435765462</v>
+        <v>13.04374774346231</v>
       </c>
       <c r="O11" t="n">
-        <v>3.612701808571338</v>
+        <v>3.61161290055597</v>
       </c>
       <c r="P11" t="n">
-        <v>333.4994655846206</v>
+        <v>333.5097256226086</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -33252,7 +33304,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L610"/>
+  <dimension ref="A1:L611"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -71071,6 +71123,68 @@
         </is>
       </c>
     </row>
+    <row r="611">
+      <c r="A611" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:05:33+00:00</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>-36.60175947481665,174.70837467200943</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>-36.6024467831344,174.70865644244776</t>
+        </is>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>-36.60308425234312,174.70911118947203</t>
+        </is>
+      </c>
+      <c r="E611" t="inlineStr">
+        <is>
+          <t>-36.6037018030664,174.70962776071016</t>
+        </is>
+      </c>
+      <c r="F611" t="inlineStr">
+        <is>
+          <t>-36.60432536266625,174.71010058993994</t>
+        </is>
+      </c>
+      <c r="G611" t="inlineStr">
+        <is>
+          <t>-36.60493816447749,174.7105747876946</t>
+        </is>
+      </c>
+      <c r="H611" t="inlineStr">
+        <is>
+          <t>-36.605558076680914,174.71103473098452</t>
+        </is>
+      </c>
+      <c r="I611" t="inlineStr">
+        <is>
+          <t>-36.6061722293329,174.7115246730977</t>
+        </is>
+      </c>
+      <c r="J611" t="inlineStr">
+        <is>
+          <t>-36.60678843265591,174.71201717122528</t>
+        </is>
+      </c>
+      <c r="K611" t="inlineStr">
+        <is>
+          <t>-36.60741186100161,174.71248466093851</t>
+        </is>
+      </c>
+      <c r="L611" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0141/nzd0141.xlsx
+++ b/data/nzd0141/nzd0141.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L611"/>
+  <dimension ref="A1:L612"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26106,6 +26106,48 @@
         <v>330.19</v>
       </c>
       <c r="L611" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:11:35+00:00</t>
+        </is>
+      </c>
+      <c r="B612" t="n">
+        <v>320.32</v>
+      </c>
+      <c r="C612" t="n">
+        <v>316.85</v>
+      </c>
+      <c r="D612" t="n">
+        <v>328.31</v>
+      </c>
+      <c r="E612" t="n">
+        <v>338.36</v>
+      </c>
+      <c r="F612" t="n">
+        <v>338.95</v>
+      </c>
+      <c r="G612" t="n">
+        <v>342.13</v>
+      </c>
+      <c r="H612" t="n">
+        <v>344.14</v>
+      </c>
+      <c r="I612" t="n">
+        <v>345.72</v>
+      </c>
+      <c r="J612" t="n">
+        <v>338.79</v>
+      </c>
+      <c r="K612" t="n">
+        <v>329.9</v>
+      </c>
+      <c r="L612" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -26122,7 +26164,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B625"/>
+  <dimension ref="A1:B626"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32375,6 +32417,16 @@
       </c>
       <c r="B625" t="n">
         <v>1.24</v>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B626" t="n">
+        <v>-0.82</v>
       </c>
     </row>
   </sheetData>
@@ -32543,28 +32595,28 @@
         <v>0.0356</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.001516391447090328</v>
+        <v>-0.001694483703312286</v>
       </c>
       <c r="J2" t="n">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="K2" t="n">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="L2" t="n">
-        <v>7.435679243994464e-06</v>
+        <v>9.321195708400509e-06</v>
       </c>
       <c r="M2" t="n">
-        <v>3.144117603987338</v>
+        <v>3.139697657607224</v>
       </c>
       <c r="N2" t="n">
-        <v>16.85960116485345</v>
+        <v>16.83244676591996</v>
       </c>
       <c r="O2" t="n">
-        <v>4.10604446698443</v>
+        <v>4.102736497256431</v>
       </c>
       <c r="P2" t="n">
-        <v>320.8769181364937</v>
+        <v>320.8787724895848</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -32621,28 +32673,28 @@
         <v>0.0512</v>
       </c>
       <c r="I3" t="n">
-        <v>0.05599924931671564</v>
+        <v>0.05502146542055719</v>
       </c>
       <c r="J3" t="n">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="K3" t="n">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01140099554672536</v>
+        <v>0.01104389654040172</v>
       </c>
       <c r="M3" t="n">
-        <v>3.105586301342266</v>
+        <v>3.104722339860733</v>
       </c>
       <c r="N3" t="n">
-        <v>14.82485054832928</v>
+        <v>14.81382204619462</v>
       </c>
       <c r="O3" t="n">
-        <v>3.850305253915497</v>
+        <v>3.848872828010121</v>
       </c>
       <c r="P3" t="n">
-        <v>318.2087054402212</v>
+        <v>318.2188864364576</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -32699,28 +32751,28 @@
         <v>0.046</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0492367537560138</v>
+        <v>-0.04959038255875307</v>
       </c>
       <c r="J4" t="n">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="K4" t="n">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="L4" t="n">
-        <v>0.009700639095986729</v>
+        <v>0.009876306821303915</v>
       </c>
       <c r="M4" t="n">
-        <v>2.983185463726829</v>
+        <v>2.979992459151084</v>
       </c>
       <c r="N4" t="n">
-        <v>13.49253319818491</v>
+        <v>13.47218160551022</v>
       </c>
       <c r="O4" t="n">
-        <v>3.673218370609745</v>
+        <v>3.670447057990378</v>
       </c>
       <c r="P4" t="n">
-        <v>330.6555421282503</v>
+        <v>330.6592242235722</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -32777,28 +32829,28 @@
         <v>0.0417</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.08717528282496267</v>
+        <v>-0.08730253739716769</v>
       </c>
       <c r="J5" t="n">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="K5" t="n">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02784447151011971</v>
+        <v>0.02803026596083158</v>
       </c>
       <c r="M5" t="n">
-        <v>2.845040411912783</v>
+        <v>2.840949677177279</v>
       </c>
       <c r="N5" t="n">
-        <v>14.46545243754538</v>
+        <v>14.44200156236478</v>
       </c>
       <c r="O5" t="n">
-        <v>3.803347530471727</v>
+        <v>3.800263354343326</v>
       </c>
       <c r="P5" t="n">
-        <v>341.0500780378991</v>
+        <v>341.0514030528904</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -32855,28 +32907,28 @@
         <v>0.0408</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.06395527766545368</v>
+        <v>-0.06421270298931511</v>
       </c>
       <c r="J6" t="n">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="K6" t="n">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01639029002041503</v>
+        <v>0.01658332803677565</v>
       </c>
       <c r="M6" t="n">
-        <v>2.875755823013425</v>
+        <v>2.872285925939196</v>
       </c>
       <c r="N6" t="n">
-        <v>13.38250663190294</v>
+        <v>13.36152134740467</v>
       </c>
       <c r="O6" t="n">
-        <v>3.658210851208954</v>
+        <v>3.655341481640897</v>
       </c>
       <c r="P6" t="n">
-        <v>341.4026991352047</v>
+        <v>341.4053795293732</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -32933,28 +32985,28 @@
         <v>0.0371</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.06493235508386448</v>
+        <v>-0.06442197151347966</v>
       </c>
       <c r="J7" t="n">
+        <v>611</v>
+      </c>
+      <c r="K7" t="n">
         <v>610</v>
       </c>
-      <c r="K7" t="n">
-        <v>609</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.0161631597968207</v>
+        <v>0.01597181358259081</v>
       </c>
       <c r="M7" t="n">
-        <v>2.888181856714403</v>
+        <v>2.885385119599062</v>
       </c>
       <c r="N7" t="n">
-        <v>13.99724906807157</v>
+        <v>13.97791234486473</v>
       </c>
       <c r="O7" t="n">
-        <v>3.74128975997203</v>
+        <v>3.738704634611395</v>
       </c>
       <c r="P7" t="n">
-        <v>342.3747227212996</v>
+        <v>342.3694062828782</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -33011,28 +33063,28 @@
         <v>0.0403</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.02047041002375641</v>
+        <v>-0.02044563163389975</v>
       </c>
       <c r="J8" t="n">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="K8" t="n">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="L8" t="n">
-        <v>0.002361301685909201</v>
+        <v>0.002364876711081654</v>
       </c>
       <c r="M8" t="n">
-        <v>2.357228866807048</v>
+        <v>2.353500109857428</v>
       </c>
       <c r="N8" t="n">
-        <v>9.65213558595886</v>
+        <v>9.636346809207179</v>
       </c>
       <c r="O8" t="n">
-        <v>3.106788629108659</v>
+        <v>3.104246576740833</v>
       </c>
       <c r="P8" t="n">
-        <v>344.6112747351183</v>
+        <v>344.6110167346595</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -33089,28 +33141,28 @@
         <v>0.046</v>
       </c>
       <c r="I9" t="n">
-        <v>0.02229270140600487</v>
+        <v>0.02141879616632706</v>
       </c>
       <c r="J9" t="n">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="K9" t="n">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="L9" t="n">
-        <v>0.002322581454335726</v>
+        <v>0.002150930619767566</v>
       </c>
       <c r="M9" t="n">
-        <v>2.584009174523568</v>
+        <v>2.583349997818979</v>
       </c>
       <c r="N9" t="n">
-        <v>11.63839538873534</v>
+        <v>11.62991931985509</v>
       </c>
       <c r="O9" t="n">
-        <v>3.411509253795941</v>
+        <v>3.410266752008571</v>
       </c>
       <c r="P9" t="n">
-        <v>347.6715829930745</v>
+        <v>347.6806823717728</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -33167,28 +33219,28 @@
         <v>0.0509</v>
       </c>
       <c r="I10" t="n">
-        <v>0.03700889656971363</v>
+        <v>0.03585749279462491</v>
       </c>
       <c r="J10" t="n">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="K10" t="n">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0062586748896033</v>
+        <v>0.005891536260588692</v>
       </c>
       <c r="M10" t="n">
-        <v>2.774288962783998</v>
+        <v>2.776533917748179</v>
       </c>
       <c r="N10" t="n">
-        <v>11.85637022535846</v>
+        <v>11.85531745143703</v>
       </c>
       <c r="O10" t="n">
-        <v>3.443308035212427</v>
+        <v>3.4431551593614</v>
       </c>
       <c r="P10" t="n">
-        <v>341.1622642645957</v>
+        <v>341.1742530461117</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -33245,28 +33297,28 @@
         <v>0.0522</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.01695930468857033</v>
+        <v>-0.01804087315446466</v>
       </c>
       <c r="J11" t="n">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="K11" t="n">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="L11" t="n">
-        <v>0.00120071638491015</v>
+        <v>0.001362198856520558</v>
       </c>
       <c r="M11" t="n">
-        <v>2.921143686340968</v>
+        <v>2.921558200438621</v>
       </c>
       <c r="N11" t="n">
-        <v>13.04374774346231</v>
+        <v>13.0385929533933</v>
       </c>
       <c r="O11" t="n">
-        <v>3.61161290055597</v>
+        <v>3.610899189037725</v>
       </c>
       <c r="P11" t="n">
-        <v>333.5097256226086</v>
+        <v>333.5209872567223</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -33304,7 +33356,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L611"/>
+  <dimension ref="A1:L612"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -71185,6 +71237,68 @@
         </is>
       </c>
     </row>
+    <row r="612">
+      <c r="A612" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:11:35+00:00</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>-36.601757583971896,174.70838023378028</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>-36.60243729385079,174.70868435451723</t>
+        </is>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>-36.6030715861132,174.70914591825223</t>
+        </is>
+      </c>
+      <c r="E612" t="inlineStr">
+        <is>
+          <t>-36.603697704065425,174.70963721085977</t>
+        </is>
+      </c>
+      <c r="F612" t="inlineStr">
+        <is>
+          <t>-36.60432628381418,174.71009866830374</t>
+        </is>
+      </c>
+      <c r="G612" t="inlineStr">
+        <is>
+          <t>-36.60493567188799,174.7105799720974</t>
+        </is>
+      </c>
+      <c r="H612" t="inlineStr">
+        <is>
+          <t>-36.60554963649671,174.71105217536606</t>
+        </is>
+      </c>
+      <c r="I612" t="inlineStr">
+        <is>
+          <t>-36.606170704317286,174.71152744224062</t>
+        </is>
+      </c>
+      <c r="J612" t="inlineStr">
+        <is>
+          <t>-36.60679131009862,174.7120125831167</t>
+        </is>
+      </c>
+      <c r="K612" t="inlineStr">
+        <is>
+          <t>-36.60741347498876,174.7124821111413</t>
+        </is>
+      </c>
+      <c r="L612" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0141/nzd0141.xlsx
+++ b/data/nzd0141/nzd0141.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L612"/>
+  <dimension ref="A1:L618"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26148,6 +26148,258 @@
         <v>329.9</v>
       </c>
       <c r="L612" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:11:20+00:00</t>
+        </is>
+      </c>
+      <c r="B613" t="n">
+        <v>320.12</v>
+      </c>
+      <c r="C613" t="n">
+        <v>317.13</v>
+      </c>
+      <c r="D613" t="n">
+        <v>328.75</v>
+      </c>
+      <c r="E613" t="n">
+        <v>338.53</v>
+      </c>
+      <c r="F613" t="n">
+        <v>338.93</v>
+      </c>
+      <c r="G613" t="n">
+        <v>342.15</v>
+      </c>
+      <c r="H613" t="n">
+        <v>343.84</v>
+      </c>
+      <c r="I613" t="n">
+        <v>346.15</v>
+      </c>
+      <c r="J613" t="n">
+        <v>339.36</v>
+      </c>
+      <c r="K613" t="n">
+        <v>331.13</v>
+      </c>
+      <c r="L613" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:11:30+00:00</t>
+        </is>
+      </c>
+      <c r="B614" t="n">
+        <v>318.59</v>
+      </c>
+      <c r="C614" t="n">
+        <v>316.65</v>
+      </c>
+      <c r="D614" t="n">
+        <v>327.5</v>
+      </c>
+      <c r="E614" t="n">
+        <v>336.89</v>
+      </c>
+      <c r="F614" t="n">
+        <v>337.26</v>
+      </c>
+      <c r="G614" t="n">
+        <v>340.15</v>
+      </c>
+      <c r="H614" t="n">
+        <v>342.98</v>
+      </c>
+      <c r="I614" t="n">
+        <v>345.51</v>
+      </c>
+      <c r="J614" t="n">
+        <v>338.34</v>
+      </c>
+      <c r="K614" t="n">
+        <v>330.42</v>
+      </c>
+      <c r="L614" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B615" t="n">
+        <v>317.48</v>
+      </c>
+      <c r="C615" t="n">
+        <v>316.77</v>
+      </c>
+      <c r="D615" t="n">
+        <v>327.6</v>
+      </c>
+      <c r="E615" t="n">
+        <v>336.46</v>
+      </c>
+      <c r="F615" t="n">
+        <v>336.56</v>
+      </c>
+      <c r="G615" t="n">
+        <v>338.81</v>
+      </c>
+      <c r="H615" t="n">
+        <v>342.9</v>
+      </c>
+      <c r="I615" t="n">
+        <v>346.06</v>
+      </c>
+      <c r="J615" t="n">
+        <v>337.28</v>
+      </c>
+      <c r="K615" t="n">
+        <v>329.96</v>
+      </c>
+      <c r="L615" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B616" t="n">
+        <v>316.99</v>
+      </c>
+      <c r="C616" t="n">
+        <v>316.5</v>
+      </c>
+      <c r="D616" t="n">
+        <v>327.09</v>
+      </c>
+      <c r="E616" t="n">
+        <v>335.79</v>
+      </c>
+      <c r="F616" t="n">
+        <v>335.67</v>
+      </c>
+      <c r="G616" t="n">
+        <v>337.45</v>
+      </c>
+      <c r="H616" t="n">
+        <v>342.65</v>
+      </c>
+      <c r="I616" t="n">
+        <v>345.98</v>
+      </c>
+      <c r="J616" t="n">
+        <v>337.26</v>
+      </c>
+      <c r="K616" t="n">
+        <v>329.97</v>
+      </c>
+      <c r="L616" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:05:08+00:00</t>
+        </is>
+      </c>
+      <c r="B617" t="n">
+        <v>316.21</v>
+      </c>
+      <c r="C617" t="n">
+        <v>316</v>
+      </c>
+      <c r="D617" t="n">
+        <v>326.76</v>
+      </c>
+      <c r="E617" t="n">
+        <v>335.18</v>
+      </c>
+      <c r="F617" t="n">
+        <v>335.18</v>
+      </c>
+      <c r="G617" t="n">
+        <v>336.77</v>
+      </c>
+      <c r="H617" t="n">
+        <v>342.31</v>
+      </c>
+      <c r="I617" t="n">
+        <v>345.69</v>
+      </c>
+      <c r="J617" t="n">
+        <v>337.01</v>
+      </c>
+      <c r="K617" t="n">
+        <v>329.61</v>
+      </c>
+      <c r="L617" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:04:56+00:00</t>
+        </is>
+      </c>
+      <c r="B618" t="n">
+        <v>316.74</v>
+      </c>
+      <c r="C618" t="n">
+        <v>316.15</v>
+      </c>
+      <c r="D618" t="n">
+        <v>326.85</v>
+      </c>
+      <c r="E618" t="n">
+        <v>335.07</v>
+      </c>
+      <c r="F618" t="n">
+        <v>335.35</v>
+      </c>
+      <c r="G618" t="n">
+        <v>336.7</v>
+      </c>
+      <c r="H618" t="n">
+        <v>342.68</v>
+      </c>
+      <c r="I618" t="n">
+        <v>346.17</v>
+      </c>
+      <c r="J618" t="n">
+        <v>338.36</v>
+      </c>
+      <c r="K618" t="n">
+        <v>329.73</v>
+      </c>
+      <c r="L618" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -26164,7 +26416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B626"/>
+  <dimension ref="A1:B632"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32427,6 +32679,66 @@
       </c>
       <c r="B626" t="n">
         <v>-0.82</v>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B627" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B628" t="n">
+        <v>-0.27</v>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B629" t="n">
+        <v>-0.02</v>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B630" t="n">
+        <v>-0.19</v>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B631" t="n">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B632" t="n">
+        <v>-0.87</v>
       </c>
     </row>
   </sheetData>
@@ -32595,28 +32907,28 @@
         <v>0.0356</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.001694483703312286</v>
+        <v>-0.008000332803544495</v>
       </c>
       <c r="J2" t="n">
-        <v>611</v>
+        <v>617</v>
       </c>
       <c r="K2" t="n">
-        <v>611</v>
+        <v>617</v>
       </c>
       <c r="L2" t="n">
-        <v>9.321195708400509e-06</v>
+        <v>0.0002112559800996339</v>
       </c>
       <c r="M2" t="n">
-        <v>3.139697657607224</v>
+        <v>3.134680202170283</v>
       </c>
       <c r="N2" t="n">
-        <v>16.83244676591996</v>
+        <v>16.77858801805237</v>
       </c>
       <c r="O2" t="n">
-        <v>4.102736497256431</v>
+        <v>4.096167479248422</v>
       </c>
       <c r="P2" t="n">
-        <v>320.8787724895848</v>
+        <v>320.944647431239</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -32673,28 +32985,28 @@
         <v>0.0512</v>
       </c>
       <c r="I3" t="n">
-        <v>0.05502146542055719</v>
+        <v>0.04870101679043463</v>
       </c>
       <c r="J3" t="n">
-        <v>611</v>
+        <v>617</v>
       </c>
       <c r="K3" t="n">
-        <v>611</v>
+        <v>617</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01104389654040172</v>
+        <v>0.008819430349289226</v>
       </c>
       <c r="M3" t="n">
-        <v>3.104722339860733</v>
+        <v>3.101620923591806</v>
       </c>
       <c r="N3" t="n">
-        <v>14.81382204619462</v>
+        <v>14.76482739868042</v>
       </c>
       <c r="O3" t="n">
-        <v>3.848872828010121</v>
+        <v>3.842502751941816</v>
       </c>
       <c r="P3" t="n">
-        <v>318.2188864364576</v>
+        <v>318.2848907273674</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -32751,28 +33063,28 @@
         <v>0.046</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.04959038255875307</v>
+        <v>-0.05341787832482289</v>
       </c>
       <c r="J4" t="n">
-        <v>611</v>
+        <v>617</v>
       </c>
       <c r="K4" t="n">
-        <v>611</v>
+        <v>617</v>
       </c>
       <c r="L4" t="n">
-        <v>0.009876306821303915</v>
+        <v>0.01167517581484012</v>
       </c>
       <c r="M4" t="n">
-        <v>2.979992459151084</v>
+        <v>2.969122651196618</v>
       </c>
       <c r="N4" t="n">
-        <v>13.47218160551022</v>
+        <v>13.37979981730144</v>
       </c>
       <c r="O4" t="n">
-        <v>3.670447057990378</v>
+        <v>3.657840868231072</v>
       </c>
       <c r="P4" t="n">
-        <v>330.6592242235722</v>
+        <v>330.699205044641</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -32829,28 +33141,28 @@
         <v>0.0417</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.08730253739716769</v>
+        <v>-0.09211594966774363</v>
       </c>
       <c r="J5" t="n">
-        <v>611</v>
+        <v>617</v>
       </c>
       <c r="K5" t="n">
-        <v>611</v>
+        <v>617</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02803026596083158</v>
+        <v>0.03167350220036258</v>
       </c>
       <c r="M5" t="n">
-        <v>2.840949677177279</v>
+        <v>2.834413930677679</v>
       </c>
       <c r="N5" t="n">
-        <v>14.44200156236478</v>
+        <v>14.3692952751556</v>
       </c>
       <c r="O5" t="n">
-        <v>3.800263354343326</v>
+        <v>3.790685330537949</v>
       </c>
       <c r="P5" t="n">
-        <v>341.0514030528904</v>
+        <v>341.1016922286432</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -32907,28 +33219,28 @@
         <v>0.0408</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.06421270298931511</v>
+        <v>-0.07062598730172108</v>
       </c>
       <c r="J6" t="n">
-        <v>611</v>
+        <v>617</v>
       </c>
       <c r="K6" t="n">
-        <v>611</v>
+        <v>617</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01658332803677565</v>
+        <v>0.02028479023185592</v>
       </c>
       <c r="M6" t="n">
-        <v>2.872285925939196</v>
+        <v>2.874700938325377</v>
       </c>
       <c r="N6" t="n">
-        <v>13.36152134740467</v>
+        <v>13.34438199486227</v>
       </c>
       <c r="O6" t="n">
-        <v>3.655341481640897</v>
+        <v>3.652996303702245</v>
       </c>
       <c r="P6" t="n">
-        <v>341.4053795293732</v>
+        <v>341.4723767837269</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -32985,28 +33297,28 @@
         <v>0.0371</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.06442197151347966</v>
+        <v>-0.06839351664960949</v>
       </c>
       <c r="J7" t="n">
-        <v>611</v>
+        <v>617</v>
       </c>
       <c r="K7" t="n">
-        <v>610</v>
+        <v>616</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01597181358259081</v>
+        <v>0.01828475997350965</v>
       </c>
       <c r="M7" t="n">
-        <v>2.885385119599062</v>
+        <v>2.884947426775067</v>
       </c>
       <c r="N7" t="n">
-        <v>13.97791234486473</v>
+        <v>13.91637327850753</v>
       </c>
       <c r="O7" t="n">
-        <v>3.738704634611395</v>
+        <v>3.730465557877131</v>
       </c>
       <c r="P7" t="n">
-        <v>342.3694062828782</v>
+        <v>342.4109425202054</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -33063,28 +33375,28 @@
         <v>0.0403</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.02044563163389975</v>
+        <v>-0.02279782250819973</v>
       </c>
       <c r="J8" t="n">
-        <v>611</v>
+        <v>617</v>
       </c>
       <c r="K8" t="n">
-        <v>611</v>
+        <v>617</v>
       </c>
       <c r="L8" t="n">
-        <v>0.002364876711081654</v>
+        <v>0.003003055423567269</v>
       </c>
       <c r="M8" t="n">
-        <v>2.353500109857428</v>
+        <v>2.340638453763771</v>
       </c>
       <c r="N8" t="n">
-        <v>9.636346809207179</v>
+        <v>9.557785689410998</v>
       </c>
       <c r="O8" t="n">
-        <v>3.104246576740833</v>
+        <v>3.09156686639817</v>
       </c>
       <c r="P8" t="n">
-        <v>344.6110167346595</v>
+        <v>344.6355878111524</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -33141,28 +33453,28 @@
         <v>0.046</v>
       </c>
       <c r="I9" t="n">
-        <v>0.02141879616632706</v>
+        <v>0.0167591230660014</v>
       </c>
       <c r="J9" t="n">
-        <v>611</v>
+        <v>617</v>
       </c>
       <c r="K9" t="n">
-        <v>611</v>
+        <v>617</v>
       </c>
       <c r="L9" t="n">
-        <v>0.002150930619767566</v>
+        <v>0.001343036285616495</v>
       </c>
       <c r="M9" t="n">
-        <v>2.583349997818979</v>
+        <v>2.57734754976975</v>
       </c>
       <c r="N9" t="n">
-        <v>11.62991931985509</v>
+        <v>11.56834522897638</v>
       </c>
       <c r="O9" t="n">
-        <v>3.410266752008571</v>
+        <v>3.401227018147477</v>
       </c>
       <c r="P9" t="n">
-        <v>347.6806823717728</v>
+        <v>347.7293360172147</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -33219,28 +33531,28 @@
         <v>0.0509</v>
       </c>
       <c r="I10" t="n">
-        <v>0.03585749279462491</v>
+        <v>0.02745196550679721</v>
       </c>
       <c r="J10" t="n">
-        <v>611</v>
+        <v>617</v>
       </c>
       <c r="K10" t="n">
-        <v>611</v>
+        <v>617</v>
       </c>
       <c r="L10" t="n">
-        <v>0.005891536260588692</v>
+        <v>0.003491965512130935</v>
       </c>
       <c r="M10" t="n">
-        <v>2.776533917748179</v>
+        <v>2.798968981885468</v>
       </c>
       <c r="N10" t="n">
-        <v>11.85531745143703</v>
+        <v>11.91236028359651</v>
       </c>
       <c r="O10" t="n">
-        <v>3.4431551593614</v>
+        <v>3.451428730771724</v>
       </c>
       <c r="P10" t="n">
-        <v>341.1742530461117</v>
+        <v>341.2620333948644</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -33297,28 +33609,28 @@
         <v>0.0522</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.01804087315446466</v>
+        <v>-0.02385910729820529</v>
       </c>
       <c r="J11" t="n">
-        <v>611</v>
+        <v>617</v>
       </c>
       <c r="K11" t="n">
-        <v>611</v>
+        <v>617</v>
       </c>
       <c r="L11" t="n">
-        <v>0.001362198856520558</v>
+        <v>0.002420825512883029</v>
       </c>
       <c r="M11" t="n">
-        <v>2.921558200438621</v>
+        <v>2.92101660036531</v>
       </c>
       <c r="N11" t="n">
-        <v>13.0385929533933</v>
+        <v>12.9936851497512</v>
       </c>
       <c r="O11" t="n">
-        <v>3.610899189037725</v>
+        <v>3.604675456924131</v>
       </c>
       <c r="P11" t="n">
-        <v>333.5209872567223</v>
+        <v>333.5817512617064</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -33356,7 +33668,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L612"/>
+  <dimension ref="A1:L618"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -71299,6 +71611,378 @@
         </is>
       </c>
     </row>
+    <row r="613">
+      <c r="A613" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:11:20+00:00</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>-36.60175828428479,174.70837817386516</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>-36.60243631340784,174.70868723842068</t>
+        </is>
+      </c>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>-36.603069951760226,174.70915039938433</t>
+        </is>
+      </c>
+      <c r="E613" t="inlineStr">
+        <is>
+          <t>-36.60369697820058,174.70963888432365</t>
+        </is>
+      </c>
+      <c r="F613" t="inlineStr">
+        <is>
+          <t>-36.60432637592897,174.71009847614013</t>
+        </is>
+      </c>
+      <c r="G613" t="inlineStr">
+        <is>
+          <t>-36.60493557956986,174.7105801641123</t>
+        </is>
+      </c>
+      <c r="H613" t="inlineStr">
+        <is>
+          <t>-36.605551027736034,174.71104929991884</t>
+        </is>
+      </c>
+      <c r="I613" t="inlineStr">
+        <is>
+          <t>-36.606168518461466,174.71153141134525</t>
+        </is>
+      </c>
+      <c r="J613" t="inlineStr">
+        <is>
+          <t>-36.60678815597871,174.7120176123896</t>
+        </is>
+      </c>
+      <c r="K613" t="inlineStr">
+        <is>
+          <t>-36.60740662945666,174.7124929257977</t>
+        </is>
+      </c>
+      <c r="L613" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:11:30+00:00</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>-36.601763641677366,174.70836241551342</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>-36.60243799416714,174.70868229458617</t>
+        </is>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>-36.60307459480799,174.70913766889495</t>
+        </is>
+      </c>
+      <c r="E614" t="inlineStr">
+        <is>
+          <t>-36.60370398066038,174.70962274031777</t>
+        </is>
+      </c>
+      <c r="F614" t="inlineStr">
+        <is>
+          <t>-36.60433406751299,174.71008243047618</t>
+        </is>
+      </c>
+      <c r="G614" t="inlineStr">
+        <is>
+          <t>-36.60494481138173,174.7105609626188</t>
+        </is>
+      </c>
+      <c r="H614" t="inlineStr">
+        <is>
+          <t>-36.60555501595506,174.7110410569695</t>
+        </is>
+      </c>
+      <c r="I614" t="inlineStr">
+        <is>
+          <t>-36.60617177182822,174.7115255038406</t>
+        </is>
+      </c>
+      <c r="J614" t="inlineStr">
+        <is>
+          <t>-36.60679380019314,174.71200861263782</t>
+        </is>
+      </c>
+      <c r="K614" t="inlineStr">
+        <is>
+          <t>-36.60741058094279,174.7124866831914</t>
+        </is>
+      </c>
+      <c r="L614" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>-36.601767528411855,174.70835098298232</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>-36.60243757397732,174.7086835305448</t>
+        </is>
+      </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>-36.60307422336423,174.70913868733416</t>
+        </is>
+      </c>
+      <c r="E615" t="inlineStr">
+        <is>
+          <t>-36.60370581667083,174.70961850743768</t>
+        </is>
+      </c>
+      <c r="F615" t="inlineStr">
+        <is>
+          <t>-36.60433729152962,174.71007570474782</t>
+        </is>
+      </c>
+      <c r="G615" t="inlineStr">
+        <is>
+          <t>-36.604950996694,174.7105480976156</t>
+        </is>
+      </c>
+      <c r="H615" t="inlineStr">
+        <is>
+          <t>-36.605555386952155,174.71104029018346</t>
+        </is>
+      </c>
+      <c r="I615" t="inlineStr">
+        <is>
+          <t>-36.60616897596618,174.71153058060244</t>
+        </is>
+      </c>
+      <c r="J615" t="inlineStr">
+        <is>
+          <t>-36.6067996657486,174.7119992599532</t>
+        </is>
+      </c>
+      <c r="K615" t="inlineStr">
+        <is>
+          <t>-36.607413141060384,174.71248263868557</t>
+        </is>
+      </c>
+      <c r="L615" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>-36.6017692441772,174.70834593618892</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>-36.60243851940439,174.7086807496378</t>
+        </is>
+      </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>-36.60307611772738,174.70913349329408</t>
+        </is>
+      </c>
+      <c r="E616" t="inlineStr">
+        <is>
+          <t>-36.60370867743101,174.70961191201945</t>
+        </is>
+      </c>
+      <c r="F616" t="inlineStr">
+        <is>
+          <t>-36.60434139063595,174.71006715346377</t>
+        </is>
+      </c>
+      <c r="G616" t="inlineStr">
+        <is>
+          <t>-36.60495727432301,174.71053504059523</t>
+        </is>
+      </c>
+      <c r="H616" t="inlineStr">
+        <is>
+          <t>-36.60555654631802,174.71103789397708</t>
+        </is>
+      </c>
+      <c r="I616" t="inlineStr">
+        <is>
+          <t>-36.60616938263703,174.71152984216437</t>
+        </is>
+      </c>
+      <c r="J616" t="inlineStr">
+        <is>
+          <t>-36.60679977641946,174.7119990834874</t>
+        </is>
+      </c>
+      <c r="K616" t="inlineStr">
+        <is>
+          <t>-36.60741308540566,174.7124827266096</t>
+        </is>
+      </c>
+      <c r="L616" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:05:08+00:00</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>-36.601771975395074,174.70833790251734</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>-36.602440270195046,174.70867559980988</t>
+        </is>
+      </c>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>-36.60307734349166,174.7091301324445</t>
+        </is>
+      </c>
+      <c r="E617" t="inlineStr">
+        <is>
+          <t>-36.60371128200341,174.7096059072353</t>
+        </is>
+      </c>
+      <c r="F617" t="inlineStr">
+        <is>
+          <t>-36.60434364744705,174.71006244545308</t>
+        </is>
+      </c>
+      <c r="G617" t="inlineStr">
+        <is>
+          <t>-36.60496041313701,174.71052851208427</t>
+        </is>
+      </c>
+      <c r="H617" t="inlineStr">
+        <is>
+          <t>-36.60555812305556,174.7110346351363</t>
+        </is>
+      </c>
+      <c r="I617" t="inlineStr">
+        <is>
+          <t>-36.60617085681884,174.71152716532634</t>
+        </is>
+      </c>
+      <c r="J617" t="inlineStr">
+        <is>
+          <t>-36.60680115980507,174.71199687766537</t>
+        </is>
+      </c>
+      <c r="K617" t="inlineStr">
+        <is>
+          <t>-36.60741508897586,174.712479561344</t>
+        </is>
+      </c>
+      <c r="L617" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:04:56+00:00</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>-36.601770119567604,174.70834336129425</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>-36.60243974495787,174.70867714475827</t>
+        </is>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>-36.60307700919231,174.70913104903985</t>
+        </is>
+      </c>
+      <c r="E618" t="inlineStr">
+        <is>
+          <t>-36.60371175168037,174.70960482440532</t>
+        </is>
+      </c>
+      <c r="F618" t="inlineStr">
+        <is>
+          <t>-36.60434286447179,174.7100640788446</t>
+        </is>
+      </c>
+      <c r="G618" t="inlineStr">
+        <is>
+          <t>-36.60496073625018,174.7105278400316</t>
+        </is>
+      </c>
+      <c r="H618" t="inlineStr">
+        <is>
+          <t>-36.605556407194136,174.71103818152187</t>
+        </is>
+      </c>
+      <c r="I618" t="inlineStr">
+        <is>
+          <t>-36.60616841679374,174.71153159595477</t>
+        </is>
+      </c>
+      <c r="J618" t="inlineStr">
+        <is>
+          <t>-36.60679368952227,174.71200878910352</t>
+        </is>
+      </c>
+      <c r="K618" t="inlineStr">
+        <is>
+          <t>-36.60741442111913,174.71248061643254</t>
+        </is>
+      </c>
+      <c r="L618" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0141/nzd0141.xlsx
+++ b/data/nzd0141/nzd0141.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L618"/>
+  <dimension ref="A1:L622"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26400,6 +26400,174 @@
         <v>329.73</v>
       </c>
       <c r="L618" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:54+00:00</t>
+        </is>
+      </c>
+      <c r="B619" t="n">
+        <v>315.34</v>
+      </c>
+      <c r="C619" t="n">
+        <v>316.48</v>
+      </c>
+      <c r="D619" t="n">
+        <v>326.76</v>
+      </c>
+      <c r="E619" t="n">
+        <v>334.07</v>
+      </c>
+      <c r="F619" t="n">
+        <v>334.57</v>
+      </c>
+      <c r="G619" t="n">
+        <v>335.43</v>
+      </c>
+      <c r="H619" t="n">
+        <v>342.63</v>
+      </c>
+      <c r="I619" t="n">
+        <v>346.6</v>
+      </c>
+      <c r="J619" t="n">
+        <v>339.16</v>
+      </c>
+      <c r="K619" t="n">
+        <v>329.53</v>
+      </c>
+      <c r="L619" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:05:18+00:00</t>
+        </is>
+      </c>
+      <c r="B620" t="n">
+        <v>316.19</v>
+      </c>
+      <c r="C620" t="n">
+        <v>316.69</v>
+      </c>
+      <c r="D620" t="n">
+        <v>327.1</v>
+      </c>
+      <c r="E620" t="n">
+        <v>335.38</v>
+      </c>
+      <c r="F620" t="n">
+        <v>335.88</v>
+      </c>
+      <c r="G620" t="n">
+        <v>336.86</v>
+      </c>
+      <c r="H620" t="n">
+        <v>343.96</v>
+      </c>
+      <c r="I620" t="n">
+        <v>348.08</v>
+      </c>
+      <c r="J620" t="n">
+        <v>341.01</v>
+      </c>
+      <c r="K620" t="n">
+        <v>330.47</v>
+      </c>
+      <c r="L620" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:11:11+00:00</t>
+        </is>
+      </c>
+      <c r="B621" t="n">
+        <v>316.83</v>
+      </c>
+      <c r="C621" t="n">
+        <v>316.86</v>
+      </c>
+      <c r="D621" t="n">
+        <v>327.1</v>
+      </c>
+      <c r="E621" t="n">
+        <v>336.13</v>
+      </c>
+      <c r="F621" t="n">
+        <v>336.61</v>
+      </c>
+      <c r="G621" t="n">
+        <v>337.83</v>
+      </c>
+      <c r="H621" t="n">
+        <v>344.55</v>
+      </c>
+      <c r="I621" t="n">
+        <v>348.86</v>
+      </c>
+      <c r="J621" t="n">
+        <v>341.79</v>
+      </c>
+      <c r="K621" t="n">
+        <v>330.98</v>
+      </c>
+      <c r="L621" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:05:30+00:00</t>
+        </is>
+      </c>
+      <c r="B622" t="n">
+        <v>316.03</v>
+      </c>
+      <c r="C622" t="n">
+        <v>316.48</v>
+      </c>
+      <c r="D622" t="n">
+        <v>326.75</v>
+      </c>
+      <c r="E622" t="n">
+        <v>335.61</v>
+      </c>
+      <c r="F622" t="n">
+        <v>336.04</v>
+      </c>
+      <c r="G622" t="n">
+        <v>337.23</v>
+      </c>
+      <c r="H622" t="n">
+        <v>344.14</v>
+      </c>
+      <c r="I622" t="n">
+        <v>348.56</v>
+      </c>
+      <c r="J622" t="n">
+        <v>342.06</v>
+      </c>
+      <c r="K622" t="n">
+        <v>330.95</v>
+      </c>
+      <c r="L622" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -26416,7 +26584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B632"/>
+  <dimension ref="A1:B636"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32739,6 +32907,46 @@
       </c>
       <c r="B632" t="n">
         <v>-0.87</v>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B633" t="n">
+        <v>-0.51</v>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B634" t="n">
+        <v>-0.87</v>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B635" t="n">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B636" t="n">
+        <v>-0.86</v>
       </c>
     </row>
   </sheetData>
@@ -32907,28 +33115,28 @@
         <v>0.0356</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.008000332803544495</v>
+        <v>-0.01410594930319426</v>
       </c>
       <c r="J2" t="n">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="K2" t="n">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0002112559800996339</v>
+        <v>0.0006611221303184367</v>
       </c>
       <c r="M2" t="n">
-        <v>3.134680202170283</v>
+        <v>3.139225069335922</v>
       </c>
       <c r="N2" t="n">
-        <v>16.77858801805237</v>
+        <v>16.80761165850704</v>
       </c>
       <c r="O2" t="n">
-        <v>4.096167479248422</v>
+        <v>4.099708728496092</v>
       </c>
       <c r="P2" t="n">
-        <v>320.944647431239</v>
+        <v>321.0086567713009</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -32985,28 +33193,28 @@
         <v>0.0512</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04870101679043463</v>
+        <v>0.04479591965479528</v>
       </c>
       <c r="J3" t="n">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="K3" t="n">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="L3" t="n">
-        <v>0.008819430349289226</v>
+        <v>0.00755771444613984</v>
       </c>
       <c r="M3" t="n">
-        <v>3.101620923591806</v>
+        <v>3.098629362044883</v>
       </c>
       <c r="N3" t="n">
-        <v>14.76482739868042</v>
+        <v>14.72522619540531</v>
       </c>
       <c r="O3" t="n">
-        <v>3.842502751941816</v>
+        <v>3.837346243878093</v>
       </c>
       <c r="P3" t="n">
-        <v>318.2848907273674</v>
+        <v>318.3258319254183</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -33063,28 +33271,28 @@
         <v>0.046</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.05341787832482289</v>
+        <v>-0.0565025495592236</v>
       </c>
       <c r="J4" t="n">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="K4" t="n">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01167517581484012</v>
+        <v>0.01320856282037919</v>
       </c>
       <c r="M4" t="n">
-        <v>2.969122651196618</v>
+        <v>2.964410519057626</v>
       </c>
       <c r="N4" t="n">
-        <v>13.37979981730144</v>
+        <v>13.32834345233055</v>
       </c>
       <c r="O4" t="n">
-        <v>3.657840868231072</v>
+        <v>3.65080038516632</v>
       </c>
       <c r="P4" t="n">
-        <v>330.699205044641</v>
+        <v>330.7315452639871</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -33141,28 +33349,28 @@
         <v>0.0417</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.09211594966774363</v>
+        <v>-0.09650881234094022</v>
       </c>
       <c r="J5" t="n">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="K5" t="n">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03167350220036258</v>
+        <v>0.03499966645622055</v>
       </c>
       <c r="M5" t="n">
-        <v>2.834413930677679</v>
+        <v>2.835748583223595</v>
       </c>
       <c r="N5" t="n">
-        <v>14.3692952751556</v>
+        <v>14.3505246657191</v>
       </c>
       <c r="O5" t="n">
-        <v>3.790685330537949</v>
+        <v>3.788208635452791</v>
       </c>
       <c r="P5" t="n">
-        <v>341.1016922286432</v>
+        <v>341.1477422658701</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -33219,28 +33427,28 @@
         <v>0.0408</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.07062598730172108</v>
+        <v>-0.075640397620724</v>
       </c>
       <c r="J6" t="n">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="K6" t="n">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02028479023185592</v>
+        <v>0.0233837325199403</v>
       </c>
       <c r="M6" t="n">
-        <v>2.874700938325377</v>
+        <v>2.879941581925236</v>
       </c>
       <c r="N6" t="n">
-        <v>13.34438199486227</v>
+        <v>13.35328151974931</v>
       </c>
       <c r="O6" t="n">
-        <v>3.652996303702245</v>
+        <v>3.654214213719457</v>
       </c>
       <c r="P6" t="n">
-        <v>341.4723767837269</v>
+        <v>341.5249434399115</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -33297,28 +33505,28 @@
         <v>0.0371</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.06839351664960949</v>
+        <v>-0.07332166772695985</v>
       </c>
       <c r="J7" t="n">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="K7" t="n">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01828475997350965</v>
+        <v>0.02113361483119292</v>
       </c>
       <c r="M7" t="n">
-        <v>2.884947426775067</v>
+        <v>2.894296656496561</v>
       </c>
       <c r="N7" t="n">
-        <v>13.91637327850753</v>
+        <v>13.91989395700692</v>
       </c>
       <c r="O7" t="n">
-        <v>3.730465557877131</v>
+        <v>3.730937409955696</v>
       </c>
       <c r="P7" t="n">
-        <v>342.4109425202054</v>
+        <v>342.462625203218</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -33375,28 +33583,28 @@
         <v>0.0403</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.02279782250819973</v>
+        <v>-0.02306769288213469</v>
       </c>
       <c r="J8" t="n">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="K8" t="n">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="L8" t="n">
-        <v>0.003003055423567269</v>
+        <v>0.003120377755928438</v>
       </c>
       <c r="M8" t="n">
-        <v>2.340638453763771</v>
+        <v>2.328780691233035</v>
       </c>
       <c r="N8" t="n">
-        <v>9.557785689410998</v>
+        <v>9.499793081226603</v>
       </c>
       <c r="O8" t="n">
-        <v>3.09156686639817</v>
+        <v>3.082173434644229</v>
       </c>
       <c r="P8" t="n">
-        <v>344.6355878111524</v>
+        <v>344.6384127512755</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -33453,28 +33661,28 @@
         <v>0.046</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0167591230660014</v>
+        <v>0.0165599005428585</v>
       </c>
       <c r="J9" t="n">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="K9" t="n">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="L9" t="n">
-        <v>0.001343036285616495</v>
+        <v>0.001330923621882918</v>
       </c>
       <c r="M9" t="n">
-        <v>2.57734754976975</v>
+        <v>2.565029391433903</v>
       </c>
       <c r="N9" t="n">
-        <v>11.56834522897638</v>
+        <v>11.49884438423543</v>
       </c>
       <c r="O9" t="n">
-        <v>3.401227018147477</v>
+        <v>3.39099460103307</v>
       </c>
       <c r="P9" t="n">
-        <v>347.7293360172147</v>
+        <v>347.7314185576731</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -33531,28 +33739,28 @@
         <v>0.0509</v>
       </c>
       <c r="I10" t="n">
-        <v>0.02745196550679721</v>
+        <v>0.02614463774917922</v>
       </c>
       <c r="J10" t="n">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="K10" t="n">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="L10" t="n">
-        <v>0.003491965512130935</v>
+        <v>0.003213029557605052</v>
       </c>
       <c r="M10" t="n">
-        <v>2.798968981885468</v>
+        <v>2.788827462299735</v>
       </c>
       <c r="N10" t="n">
-        <v>11.91236028359651</v>
+        <v>11.85013146937586</v>
       </c>
       <c r="O10" t="n">
-        <v>3.451428730771724</v>
+        <v>3.442401991252018</v>
       </c>
       <c r="P10" t="n">
-        <v>341.2620333948644</v>
+        <v>341.2757300509767</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -33609,28 +33817,28 @@
         <v>0.0522</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.02385910729820529</v>
+        <v>-0.0271036320252348</v>
       </c>
       <c r="J11" t="n">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="K11" t="n">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="L11" t="n">
-        <v>0.002420825512883029</v>
+        <v>0.003159850426287303</v>
       </c>
       <c r="M11" t="n">
-        <v>2.92101660036531</v>
+        <v>2.917613298605555</v>
       </c>
       <c r="N11" t="n">
-        <v>12.9936851497512</v>
+        <v>12.95043213806228</v>
       </c>
       <c r="O11" t="n">
-        <v>3.604675456924131</v>
+        <v>3.598670884932696</v>
       </c>
       <c r="P11" t="n">
-        <v>333.5817512617064</v>
+        <v>333.6157622167364</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -33668,7 +33876,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L618"/>
+  <dimension ref="A1:L622"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -71983,6 +72191,254 @@
         </is>
       </c>
     </row>
+    <row r="619">
+      <c r="A619" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:54+00:00</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>-36.60177502175284,174.70832894188294</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>-36.60243858943602,174.7086805436447</t>
+        </is>
+      </c>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>-36.60307734349166,174.7091301324445</t>
+        </is>
+      </c>
+      <c r="E619" t="inlineStr">
+        <is>
+          <t>-36.60371602147045,174.7095949804958</t>
+        </is>
+      </c>
+      <c r="F619" t="inlineStr">
+        <is>
+          <t>-36.604346456946324,174.71005658445978</t>
+        </is>
+      </c>
+      <c r="G619" t="inlineStr">
+        <is>
+          <t>-36.60496659844588,174.71051564707574</t>
+        </is>
+      </c>
+      <c r="H619" t="inlineStr">
+        <is>
+          <t>-36.605556639067295,174.71103770228058</t>
+        </is>
+      </c>
+      <c r="I619" t="inlineStr">
+        <is>
+          <t>-36.60616623093778,174.71153556505917</t>
+        </is>
+      </c>
+      <c r="J619" t="inlineStr">
+        <is>
+          <t>-36.606789262687464,174.7120158477325</t>
+        </is>
+      </c>
+      <c r="K619" t="inlineStr">
+        <is>
+          <t>-36.60741553421367,174.7124788579516</t>
+        </is>
+      </c>
+      <c r="L619" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:05:18+00:00</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>-36.6017720454263,174.70833769652575</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>-36.60243785410387,174.70868270657238</t>
+        </is>
+      </c>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>-36.60307608058301,174.709133595138</t>
+        </is>
+      </c>
+      <c r="E620" t="inlineStr">
+        <is>
+          <t>-36.60371042804527,174.70960787601703</t>
+        </is>
+      </c>
+      <c r="F620" t="inlineStr">
+        <is>
+          <t>-36.60434042343114,174.7100691711826</t>
+        </is>
+      </c>
+      <c r="G620" t="inlineStr">
+        <is>
+          <t>-36.604959997705755,174.71052937615192</t>
+        </is>
+      </c>
+      <c r="H620" t="inlineStr">
+        <is>
+          <t>-36.60555047124031,174.71105045009776</t>
+        </is>
+      </c>
+      <c r="I620" t="inlineStr">
+        <is>
+          <t>-36.606158707525616,174.71154922616097</t>
+        </is>
+      </c>
+      <c r="J620" t="inlineStr">
+        <is>
+          <t>-36.60677902563048,174.71203217080875</t>
+        </is>
+      </c>
+      <c r="K620" t="inlineStr">
+        <is>
+          <t>-36.607410302669116,174.71248712281158</t>
+        </is>
+      </c>
+      <c r="L620" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:11:11+00:00</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>-36.601769804427065,174.70834428825634</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>-36.60243725883497,174.70868445751378</t>
+        </is>
+      </c>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>-36.60307608058301,174.709133595138</t>
+        </is>
+      </c>
+      <c r="E621" t="inlineStr">
+        <is>
+          <t>-36.60370722570201,174.70961525894816</t>
+        </is>
+      </c>
+      <c r="F621" t="inlineStr">
+        <is>
+          <t>-36.60433706124274,174.710076185157</t>
+        </is>
+      </c>
+      <c r="G621" t="inlineStr">
+        <is>
+          <t>-36.60495552027974,174.71053868888055</t>
+        </is>
+      </c>
+      <c r="H621" t="inlineStr">
+        <is>
+          <t>-36.605547735136184,174.71105610514383</t>
+        </is>
+      </c>
+      <c r="I621" t="inlineStr">
+        <is>
+          <t>-36.606154742483454,174.71155642592973</t>
+        </is>
+      </c>
+      <c r="J621" t="inlineStr">
+        <is>
+          <t>-36.60677470946526,174.71203905296935</t>
+        </is>
+      </c>
+      <c r="K621" t="inlineStr">
+        <is>
+          <t>-36.6074074642777,174.71249160693728</t>
+        </is>
+      </c>
+      <c r="L621" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:05:30+00:00</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>-36.60177260567604,174.70833604859303</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>-36.60243858943602,174.7086805436447</t>
+        </is>
+      </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>-36.60307738063602,174.70913003060056</t>
+        </is>
+      </c>
+      <c r="E622" t="inlineStr">
+        <is>
+          <t>-36.603709445993395,174.70961014011598</t>
+        </is>
+      </c>
+      <c r="F622" t="inlineStr">
+        <is>
+          <t>-36.60433968651317,174.71007070849208</t>
+        </is>
+      </c>
+      <c r="G622" t="inlineStr">
+        <is>
+          <t>-36.604958289821695,174.71053292842998</t>
+        </is>
+      </c>
+      <c r="H622" t="inlineStr">
+        <is>
+          <t>-36.60554963649671,174.71105217536606</t>
+        </is>
+      </c>
+      <c r="I622" t="inlineStr">
+        <is>
+          <t>-36.606156267499706,174.71155365678797</t>
+        </is>
+      </c>
+      <c r="J622" t="inlineStr">
+        <is>
+          <t>-36.60677321540798,174.71204143525551</t>
+        </is>
+      </c>
+      <c r="K622" t="inlineStr">
+        <is>
+          <t>-36.607407631241905,174.7124913431652</t>
+        </is>
+      </c>
+      <c r="L622" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
